--- a/app/reporting/ldm_reports/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_98.5%_Fidelity.xlsx
+++ b/app/reporting/ldm_reports/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_98.5%_Fidelity.xlsx
@@ -758,7 +758,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP PD (PowerDesigner LDM) -&gt; erwin  |  Logical Model Validation Report   |   generated 2026-09-02 11:20</t>
+          <t>SAP PD (PowerDesigner LDM) -&gt; erwin  |  Logical Model Validation Report   |   generated 2026-09-04 16:52</t>
         </is>
       </c>
     </row>
@@ -38197,7 +38197,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>{"CHAR": "{'CHAR'}", "VARCHAR": "{'VARCHAR'}", "TEXT": "{'TEXT', 'CLOB', 'LONGTEXT', 'LONG_TEXT'}", "INTEGER": "{'INTEGER'}", "SMALLINT": "{'SMALLINT'}", "BIGINT": "{'BIGINT'}", "DECIMAL": "{'DECIMAL'}", "DATE": "{'DATE'}", "TIME": "{'TIME'}", "TIMESTAMP": "{'TIMESTAMP'}", "BINARY": "{'BINARY'}", "VARBINARY": "{'VARBINARY'}", "BOOLEAN": "{'BIT', 'BOOLEAN', 'BOOL'}", "XML": "{'XML'}"}</t>
+          <t>{"CHAR": "{'CHAR'}", "VARCHAR": "{'VARCHAR'}", "TEXT": "{'LONGTEXT', 'CLOB', 'LONG_TEXT', 'TEXT'}", "INTEGER": "{'INTEGER'}", "SMALLINT": "{'SMALLINT'}", "BIGINT": "{'BIGINT'}", "DECIMAL": "{'DECIMAL'}", "DATE": "{'DATE'}", "TIME": "{'TIME'}", "TIMESTAMP": "{'TIMESTAMP'}", "BINARY": "{'BINARY'}", "VARBINARY": "{'VARBINARY'}", "BOOLEAN": "{'BOOL', 'BOOLEAN', 'BIT'}", "XML": "{'XML'}"}</t>
         </is>
       </c>
     </row>
